--- a/results/momentum_rising_2026-10-06.xlsx
+++ b/results/momentum_rising_2026-10-06.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A83"/>
+  <dimension ref="A1:A86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,350 +426,350 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>RMBS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>OPTX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLGL</t>
+          <t>NTNX</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLIC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CRVO</t>
+          <t>VCTR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IMMP</t>
+          <t>LIND</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>COHU</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NVMI</t>
+          <t>CRVO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>ASYS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BTLN</t>
+          <t>SSTI</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XRPN</t>
+          <t>ICHR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>SHOP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ICHR</t>
+          <t>NVMI</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>SYNA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>IBRX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>NTAP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>ON</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>OKTA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CBNK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>MSGM</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>QLYS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STKE</t>
+          <t>KRNT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>AIFA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>FOSL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>DDOG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>XRPNU</t>
+          <t>SNPS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENTG</t>
+          <t>ODD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>IMMP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SILC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>REBN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CGNX</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>EVCM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>TLN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>ACLS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>LSCC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>PDFS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>NTCT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>ABLV</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>LITE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>INAB</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>BIRD</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>SOTK</t>
         </is>
       </c>
     </row>
@@ -783,217 +783,238 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>SLGL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>SANG</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MKSI</t>
+          <t>PAHC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>NMAD</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ACLS</t>
+          <t>CRWD</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASPS</t>
+          <t>IMOS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MRVL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>AXTI</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>KOD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OCC</t>
+          <t>BTLN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>FEAM</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ASYS</t>
+          <t>PXS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>PAYS</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>OPRX</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ABLV</t>
+          <t>SHLS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>STKE</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>OCG</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>LFCR</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>RXRX</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>MDAI</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>ELMT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PMVP</t>
+          <t>ENTG</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>REBN</t>
+          <t>AEHL</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>DLXY</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OPTX</t>
+          <t>MKSI</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>ENGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PACB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
